--- a/持仓.xlsx
+++ b/持仓.xlsx
@@ -1,20 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\AIGC\Stocks\CyberAdvisor\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B0EE2C9-2318-4653-B361-6F3689BB575F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
   <si>
     <t>标的</t>
   </si>
@@ -31,34 +50,40 @@
     <t>上海电力</t>
   </si>
   <si>
+    <t>600021</t>
+  </si>
+  <si>
     <t>ST美丽</t>
   </si>
   <si>
+    <t>000010</t>
+  </si>
+  <si>
     <t>电光科技</t>
   </si>
   <si>
+    <t>002730</t>
+  </si>
+  <si>
     <t>A股现金</t>
   </si>
   <si>
-    <t>600021</t>
-  </si>
-  <si>
-    <t>000010</t>
-  </si>
-  <si>
-    <t>002730</t>
+    <t>持有人</t>
+  </si>
+  <si>
+    <t>Wilson</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -90,6 +115,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -377,11 +410,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -394,13 +427,16 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C2">
         <v>19.9102</v>
@@ -408,13 +444,16 @@
       <c r="D2">
         <v>100</v>
       </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C3">
         <v>1.992</v>
@@ -422,13 +461,16 @@
       <c r="D3">
         <v>2500</v>
       </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C4">
         <v>34.7286</v>
@@ -436,13 +478,19 @@
       <c r="D4">
         <v>300</v>
       </c>
+      <c r="E4" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C5">
         <v>2.9</v>
+      </c>
+      <c r="E5" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/持仓.xlsx
+++ b/持仓.xlsx
@@ -90,19 +90,19 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -518,7 +518,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>标的</t>
         </is>
@@ -528,17 +528,17 @@
           <t>代码</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>成本</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>股数</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>持有人</t>
         </is>
@@ -560,7 +560,7 @@
       <c r="T1" s="1" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>上海电力</t>
         </is>
@@ -576,7 +576,7 @@
       <c r="D2" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Wilson</t>
         </is>
@@ -598,7 +598,7 @@
       <c r="T2" s="1" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>ST美丽</t>
         </is>
@@ -614,7 +614,7 @@
       <c r="D3" s="7" t="n">
         <v>2500</v>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Wilson</t>
         </is>
@@ -636,7 +636,7 @@
       <c r="T3" s="1" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>电光科技</t>
         </is>
@@ -652,7 +652,7 @@
       <c r="D4" s="7" t="n">
         <v>300</v>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Wilson</t>
         </is>
@@ -674,7 +674,7 @@
       <c r="T4" s="1" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>A股现金</t>
         </is>
@@ -684,7 +684,7 @@
         <v>2111.72</v>
       </c>
       <c r="D5" s="1" t="n"/>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Wilson</t>
         </is>
@@ -751,7 +751,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>300077</t>
+          <t>02701</t>
         </is>
       </c>
       <c r="C7" s="8" t="n">

--- a/持仓.xlsx
+++ b/持仓.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B5" s="10" t="n"/>
       <c r="C5" s="11" t="n">
-        <v>2111.72</v>
+        <v>350.7</v>
       </c>
       <c r="D5" s="7" t="n"/>
       <c r="E5" s="6" t="inlineStr">
